--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/175.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/175.xlsx
@@ -426,13 +426,13 @@
         <v>-14.43207071130985</v>
       </c>
       <c r="E2">
-        <v>-9.200960093966241</v>
+        <v>-9.303969292218719</v>
       </c>
       <c r="F2">
-        <v>-2.227253949074414</v>
+        <v>-1.787661734328592</v>
       </c>
       <c r="G2">
-        <v>-8.380852437156779</v>
+        <v>-8.020535971208043</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.43731822494522</v>
       </c>
       <c r="E3">
-        <v>-9.693227860970048</v>
+        <v>-10.37162496663712</v>
       </c>
       <c r="F3">
-        <v>-1.957477051902491</v>
+        <v>-1.918822943785657</v>
       </c>
       <c r="G3">
-        <v>-7.823816734173469</v>
+        <v>-8.188612368236841</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.26799854227557</v>
       </c>
       <c r="E4">
-        <v>-9.529401256794557</v>
+        <v>-10.28748591957461</v>
       </c>
       <c r="F4">
-        <v>-2.105939542934427</v>
+        <v>-1.952580572184543</v>
       </c>
       <c r="G4">
-        <v>-8.068565365891788</v>
+        <v>-7.519872237667443</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.92275980210773</v>
       </c>
       <c r="E5">
-        <v>-12.13793813943291</v>
+        <v>-11.50838968288658</v>
       </c>
       <c r="F5">
-        <v>-2.027077309453108</v>
+        <v>-1.696764150851999</v>
       </c>
       <c r="G5">
-        <v>-8.307825113105995</v>
+        <v>-8.182385232077472</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.42492860406895</v>
       </c>
       <c r="E6">
-        <v>-12.21854950524345</v>
+        <v>-11.99031441525687</v>
       </c>
       <c r="F6">
-        <v>-1.712576027836636</v>
+        <v>-1.818143169649405</v>
       </c>
       <c r="G6">
-        <v>-7.329280820426061</v>
+        <v>-8.071501819785121</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.79851595831753</v>
       </c>
       <c r="E7">
-        <v>-12.35992393528891</v>
+        <v>-12.20821552755795</v>
       </c>
       <c r="F7">
-        <v>-1.963157167183487</v>
+        <v>-1.595850777108158</v>
       </c>
       <c r="G7">
-        <v>-7.37911446242871</v>
+        <v>-7.556966900434976</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.0846647682181</v>
       </c>
       <c r="E8">
-        <v>-13.41085142672298</v>
+        <v>-13.51507878448352</v>
       </c>
       <c r="F8">
-        <v>-1.382140270859914</v>
+        <v>-1.794533870302217</v>
       </c>
       <c r="G8">
-        <v>-7.250688469323763</v>
+        <v>-7.343698246249587</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.31201454647233</v>
       </c>
       <c r="E9">
-        <v>-14.82500781831229</v>
+        <v>-15.17372295927295</v>
       </c>
       <c r="F9">
-        <v>-1.709000794126154</v>
+        <v>-1.418900731093947</v>
       </c>
       <c r="G9">
-        <v>-6.98533831271456</v>
+        <v>-7.134246651070978</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.50537929923842</v>
       </c>
       <c r="E10">
-        <v>-14.48692553432164</v>
+        <v>-15.93415337158897</v>
       </c>
       <c r="F10">
-        <v>-1.595200508696961</v>
+        <v>-1.657384392890314</v>
       </c>
       <c r="G10">
-        <v>-5.815590151868478</v>
+        <v>-6.634791266652212</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.699193702848735</v>
       </c>
       <c r="E11">
-        <v>-15.70832290130045</v>
+        <v>-16.73691595892869</v>
       </c>
       <c r="F11">
-        <v>-1.963324497398852</v>
+        <v>-1.378995788198887</v>
       </c>
       <c r="G11">
-        <v>-5.189840765672057</v>
+        <v>-5.723835071702038</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.910688023852575</v>
       </c>
       <c r="E12">
-        <v>-16.80490193920584</v>
+        <v>-17.34079702479955</v>
       </c>
       <c r="F12">
-        <v>-1.554236912261122</v>
+        <v>-1.523606370807805</v>
       </c>
       <c r="G12">
-        <v>-4.058236710529457</v>
+        <v>-5.311678773153854</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.147540440226607</v>
       </c>
       <c r="E13">
-        <v>-18.27284754505826</v>
+        <v>-18.40285550534447</v>
       </c>
       <c r="F13">
-        <v>-1.972553338633442</v>
+        <v>-1.339726203101773</v>
       </c>
       <c r="G13">
-        <v>-4.178306886693284</v>
+        <v>-4.713552578937111</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.432172880947656</v>
       </c>
       <c r="E14">
-        <v>-18.18647596030996</v>
+        <v>-18.62729573411263</v>
       </c>
       <c r="F14">
-        <v>-1.730693251303264</v>
+        <v>-1.073456613513303</v>
       </c>
       <c r="G14">
-        <v>-3.266801141183592</v>
+        <v>-4.377552069974321</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.768985902774061</v>
       </c>
       <c r="E15">
-        <v>-20.30601010570404</v>
+        <v>-19.29070359081431</v>
       </c>
       <c r="F15">
-        <v>-1.857065668804746</v>
+        <v>-1.053006707440392</v>
       </c>
       <c r="G15">
-        <v>-2.482357444016666</v>
+        <v>-3.408730849543226</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.154420095295881</v>
       </c>
       <c r="E16">
-        <v>-18.30926553302795</v>
+        <v>-20.43572824365376</v>
       </c>
       <c r="F16">
-        <v>-1.243864213780203</v>
+        <v>-0.8188148171579295</v>
       </c>
       <c r="G16">
-        <v>-2.860981226797572</v>
+        <v>-3.011885824114171</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.598481290422017</v>
       </c>
       <c r="E17">
-        <v>-20.00041056577042</v>
+        <v>-20.88345394031812</v>
       </c>
       <c r="F17">
-        <v>-1.330498190234587</v>
+        <v>-0.9126696722625163</v>
       </c>
       <c r="G17">
-        <v>-0.8342354527458982</v>
+        <v>-2.307464633722508</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.094230946922795</v>
       </c>
       <c r="E18">
-        <v>-22.02936617406307</v>
+        <v>-21.96388443991216</v>
       </c>
       <c r="F18">
-        <v>-0.9234359633967014</v>
+        <v>-1.043292442907762</v>
       </c>
       <c r="G18">
-        <v>-1.203149405460122</v>
+        <v>-1.384199830457324</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.628433699696503</v>
       </c>
       <c r="E19">
-        <v>-21.92619395074632</v>
+        <v>-22.96087327744087</v>
       </c>
       <c r="F19">
-        <v>-1.152897875809179</v>
+        <v>-0.7770195398496804</v>
       </c>
       <c r="G19">
-        <v>-0.08181135203480348</v>
+        <v>-1.499761043596664</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.201261350304652</v>
       </c>
       <c r="E20">
-        <v>-22.81839842821154</v>
+        <v>-23.06541309990794</v>
       </c>
       <c r="F20">
-        <v>-0.7863303894571468</v>
+        <v>-1.082094000422294</v>
       </c>
       <c r="G20">
-        <v>0.4622072858880914</v>
+        <v>-0.1551895939127493</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.803107967283682</v>
       </c>
       <c r="E21">
-        <v>-23.49807256354878</v>
+        <v>-24.90518264958215</v>
       </c>
       <c r="F21">
-        <v>-1.027824338395287</v>
+        <v>-0.4531659902556025</v>
       </c>
       <c r="G21">
-        <v>1.567833490184029</v>
+        <v>0.02650969801014975</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.425125276198515</v>
       </c>
       <c r="E22">
-        <v>-23.85263396445334</v>
+        <v>-24.5417680819926</v>
       </c>
       <c r="F22">
-        <v>-1.005470015663339</v>
+        <v>-0.4817695166742694</v>
       </c>
       <c r="G22">
-        <v>0.2859803257416076</v>
+        <v>0.4049381586042392</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.073837125714644</v>
       </c>
       <c r="E23">
-        <v>-23.71166256859456</v>
+        <v>-25.1212361444881</v>
       </c>
       <c r="F23">
-        <v>-1.170716058643396</v>
+        <v>-0.2980757316338679</v>
       </c>
       <c r="G23">
-        <v>1.122247302780284</v>
+        <v>0.6304657629215495</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.752402452143818</v>
       </c>
       <c r="E24">
-        <v>-24.93842617727246</v>
+        <v>-25.47679833814836</v>
       </c>
       <c r="F24">
-        <v>-0.2653436220796482</v>
+        <v>-0.5495970679828958</v>
       </c>
       <c r="G24">
-        <v>1.099960710209911</v>
+        <v>0.4955808954694843</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.466489581002883</v>
       </c>
       <c r="E25">
-        <v>-25.53358540220454</v>
+        <v>-26.47857377270317</v>
       </c>
       <c r="F25">
-        <v>-0.1370146007727544</v>
+        <v>-0.1142808857703247</v>
       </c>
       <c r="G25">
-        <v>0.4572878152167345</v>
+        <v>0.7881536680481147</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.231428517184942</v>
       </c>
       <c r="E26">
-        <v>-25.26300455177223</v>
+        <v>-26.31783558780091</v>
       </c>
       <c r="F26">
-        <v>-0.1819775550293087</v>
+        <v>-0.3393698466634232</v>
       </c>
       <c r="G26">
-        <v>1.885225422670576</v>
+        <v>0.841370687591899</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.056687044544289</v>
       </c>
       <c r="E27">
-        <v>-25.46014713922215</v>
+        <v>-26.35576608608916</v>
       </c>
       <c r="F27">
-        <v>-0.3339854585452264</v>
+        <v>-0.3118398843987845</v>
       </c>
       <c r="G27">
-        <v>2.075816839911957</v>
+        <v>1.046614579390095</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.951812634110923</v>
       </c>
       <c r="E28">
-        <v>-26.81376236180292</v>
+        <v>-25.52930146579329</v>
       </c>
       <c r="F28">
-        <v>-0.5705183151080001</v>
+        <v>-0.4675100002024787</v>
       </c>
       <c r="G28">
-        <v>1.299543569135953</v>
+        <v>0.6527291816731482</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.928615388510154</v>
       </c>
       <c r="E29">
-        <v>-26.17268441043305</v>
+        <v>-24.50538632181497</v>
       </c>
       <c r="F29">
-        <v>-0.2047543451366839</v>
+        <v>-0.04325914975650354</v>
       </c>
       <c r="G29">
-        <v>1.871105945945584</v>
+        <v>0.6797697176379153</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.990439271643912</v>
       </c>
       <c r="E30">
-        <v>-24.38985136445728</v>
+        <v>-25.79207069856237</v>
       </c>
       <c r="F30">
-        <v>-0.2661421682559469</v>
+        <v>-0.2059795005254244</v>
       </c>
       <c r="G30">
-        <v>0.7545317675512765</v>
+        <v>1.14293490185519</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.140039301165638</v>
       </c>
       <c r="E31">
-        <v>-24.84149871961228</v>
+        <v>-26.17198702543587</v>
       </c>
       <c r="F31">
-        <v>0.08885054037676722</v>
+        <v>-0.1276068321791604</v>
       </c>
       <c r="G31">
-        <v>0.1703164856905509</v>
+        <v>0.2790016957448239</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.376658369547577</v>
       </c>
       <c r="E32">
-        <v>-25.77916907611452</v>
+        <v>-24.66943029274283</v>
       </c>
       <c r="F32">
-        <v>-0.3033689993377567</v>
+        <v>-0.1389430400864716</v>
       </c>
       <c r="G32">
-        <v>0.7786226074405529</v>
+        <v>0.352992388547535</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.689693065720848</v>
       </c>
       <c r="E33">
-        <v>-24.61105373430996</v>
+        <v>-24.50766867271484</v>
       </c>
       <c r="F33">
-        <v>-0.2741400555299762</v>
+        <v>-0.1935796688729186</v>
       </c>
       <c r="G33">
-        <v>0.8430392025436917</v>
+        <v>-0.191893612306649</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.068849333110934</v>
       </c>
       <c r="E34">
-        <v>-24.07456089014724</v>
+        <v>-24.2352402048874</v>
       </c>
       <c r="F34">
-        <v>-0.4434575242947923</v>
+        <v>-0.3880579691303669</v>
       </c>
       <c r="G34">
-        <v>0.7754709680871668</v>
+        <v>0.5422562770276688</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.502662353077242</v>
       </c>
       <c r="E35">
-        <v>-24.54847928047197</v>
+        <v>-23.41521054615643</v>
       </c>
       <c r="F35">
-        <v>-0.2630589847827272</v>
+        <v>-0.2331532648068594</v>
       </c>
       <c r="G35">
-        <v>-1.793466022749725</v>
+        <v>0.23268716365042</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.970397567137337</v>
       </c>
       <c r="E36">
-        <v>-21.95299798839772</v>
+        <v>-23.43152210953206</v>
       </c>
       <c r="F36">
-        <v>-0.1598775410900207</v>
+        <v>-0.07134577491582357</v>
       </c>
       <c r="G36">
-        <v>0.8531165031652331</v>
+        <v>-1.143331158111031</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.458257253480109</v>
       </c>
       <c r="E37">
-        <v>-22.60642055991249</v>
+        <v>-22.54099769592368</v>
       </c>
       <c r="F37">
-        <v>0.005195373102850747</v>
+        <v>-0.1821432285098686</v>
       </c>
       <c r="G37">
-        <v>-0.7683258016045481</v>
+        <v>-0.8039472716071061</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.951259295514113</v>
       </c>
       <c r="E38">
-        <v>-22.10193044156199</v>
+        <v>-22.67263590685265</v>
       </c>
       <c r="F38">
-        <v>-0.3382822002635474</v>
+        <v>-0.02123120378125908</v>
       </c>
       <c r="G38">
-        <v>-0.8795866160883742</v>
+        <v>-1.649497018337899</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.428224138634258</v>
       </c>
       <c r="E39">
-        <v>-21.89501993567752</v>
+        <v>-20.81967491239409</v>
       </c>
       <c r="F39">
-        <v>0.05391580189850367</v>
+        <v>-0.1072265089680842</v>
       </c>
       <c r="G39">
-        <v>-1.073296567227749</v>
+        <v>-1.034400967686852</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.878947186345307</v>
       </c>
       <c r="E40">
-        <v>-21.80513878357328</v>
+        <v>-21.44865730968947</v>
       </c>
       <c r="F40">
-        <v>-0.1052318002621429</v>
+        <v>0.006953997098994098</v>
       </c>
       <c r="G40">
-        <v>-1.732962492474004</v>
+        <v>-1.50967943803232</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.29355815308997</v>
       </c>
       <c r="E41">
-        <v>-19.02817436716764</v>
+        <v>-20.80961264314905</v>
       </c>
       <c r="F41">
-        <v>0.1978959969138913</v>
+        <v>0.225984278808017</v>
       </c>
       <c r="G41">
-        <v>-1.479037028520826</v>
+        <v>-1.525358181706308</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.657602759633447</v>
       </c>
       <c r="E42">
-        <v>-18.77175858343132</v>
+        <v>-19.61414531833816</v>
       </c>
       <c r="F42">
-        <v>-0.290786926856635</v>
+        <v>-0.1021229373994364</v>
       </c>
       <c r="G42">
-        <v>-1.413279662474282</v>
+        <v>-1.869472837785852</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.969582574196415</v>
       </c>
       <c r="E43">
-        <v>-18.29700695388918</v>
+        <v>-18.66005018661011</v>
       </c>
       <c r="F43">
-        <v>-0.3405999722565805</v>
+        <v>0.3661970588754725</v>
       </c>
       <c r="G43">
-        <v>-1.91276815234844</v>
+        <v>-2.076434902718929</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.229562019361717</v>
       </c>
       <c r="E44">
-        <v>-18.70422545055493</v>
+        <v>-17.63810945729914</v>
       </c>
       <c r="F44">
-        <v>0.4844498190947131</v>
+        <v>0.4934251799040458</v>
       </c>
       <c r="G44">
-        <v>-2.263066907495343</v>
+        <v>-2.555371525885292</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.434280568458662</v>
       </c>
       <c r="E45">
-        <v>-16.8721814775378</v>
+        <v>-17.7686789483623</v>
       </c>
       <c r="F45">
-        <v>0.4285515867538025</v>
+        <v>0.4275650011770682</v>
       </c>
       <c r="G45">
-        <v>-1.341169359537877</v>
+        <v>-2.098148770911009</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.59077351100716</v>
       </c>
       <c r="E46">
-        <v>-16.86472760932118</v>
+        <v>-15.93141364481433</v>
       </c>
       <c r="F46">
-        <v>0.8817182581293</v>
+        <v>0.9499044925233385</v>
       </c>
       <c r="G46">
-        <v>-2.840803451735714</v>
+        <v>-3.375499593420022</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.705024018071708</v>
       </c>
       <c r="E47">
-        <v>-14.38463183496238</v>
+        <v>-16.09597386177906</v>
       </c>
       <c r="F47">
-        <v>0.7126990016294917</v>
+        <v>0.8518059112142099</v>
       </c>
       <c r="G47">
-        <v>-2.363432716609427</v>
+        <v>-3.210141154278965</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.778682403485727</v>
       </c>
       <c r="E48">
-        <v>-16.00086232219596</v>
+        <v>-15.99403338339239</v>
       </c>
       <c r="F48">
-        <v>0.8516601185513172</v>
+        <v>0.674992545821461</v>
       </c>
       <c r="G48">
-        <v>-2.266049709026226</v>
+        <v>-4.397018077745235</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.814724709621344</v>
       </c>
       <c r="E49">
-        <v>-14.76079405688352</v>
+        <v>-13.64449351467473</v>
       </c>
       <c r="F49">
-        <v>0.7318599680236471</v>
+        <v>0.3641104013878205</v>
       </c>
       <c r="G49">
-        <v>-3.133703968322733</v>
+        <v>-4.326715332673272</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.814789740441921</v>
       </c>
       <c r="E50">
-        <v>-12.51667706306442</v>
+        <v>-14.34446879898835</v>
       </c>
       <c r="F50">
-        <v>-0.02300556675805562</v>
+        <v>0.8334757973250624</v>
       </c>
       <c r="G50">
-        <v>-3.929367104322248</v>
+        <v>-4.130982638209403</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.778135613735508</v>
       </c>
       <c r="E51">
-        <v>-14.56029587019392</v>
+        <v>-12.73146258524823</v>
       </c>
       <c r="F51">
-        <v>1.220709393642136</v>
+        <v>0.6938834644423038</v>
       </c>
       <c r="G51">
-        <v>-4.018109588047952</v>
+        <v>-4.418771672483786</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.701062814423372</v>
       </c>
       <c r="E52">
-        <v>-11.40651260313602</v>
+        <v>-12.45767557521849</v>
       </c>
       <c r="F52">
-        <v>0.8109922492782782</v>
+        <v>0.8295841272667104</v>
       </c>
       <c r="G52">
-        <v>-4.14920719140309</v>
+        <v>-4.651363980981902</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.580475502218681</v>
       </c>
       <c r="E53">
-        <v>-12.5581080717606</v>
+        <v>-11.2547090974509</v>
       </c>
       <c r="F53">
-        <v>0.9811471974873247</v>
+        <v>0.8132205575918089</v>
       </c>
       <c r="G53">
-        <v>-4.71510191424949</v>
+        <v>-3.947336745509412</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.414710941445917</v>
       </c>
       <c r="E54">
-        <v>-10.89626226584775</v>
+        <v>-10.87426293911849</v>
       </c>
       <c r="F54">
-        <v>0.4783571768471228</v>
+        <v>0.4934135827604066</v>
       </c>
       <c r="G54">
-        <v>-4.239621500626126</v>
+        <v>-4.540454084325238</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.200483867966366</v>
       </c>
       <c r="E55">
-        <v>-9.487005683134747</v>
+        <v>-10.67605163180276</v>
       </c>
       <c r="F55">
-        <v>1.014553598107423</v>
+        <v>0.4932363121362075</v>
       </c>
       <c r="G55">
-        <v>-5.121494553013803</v>
+        <v>-4.940106452371595</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.934945594293073</v>
       </c>
       <c r="E56">
-        <v>-10.37960413783864</v>
+        <v>-9.443908196003749</v>
       </c>
       <c r="F56">
-        <v>0.6122851334295384</v>
+        <v>0.424954815490847</v>
       </c>
       <c r="G56">
-        <v>-5.050761437021735</v>
+        <v>-5.184298912439316</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.622326862931883</v>
       </c>
       <c r="E57">
-        <v>-10.12792060944033</v>
+        <v>-9.663267476935301</v>
       </c>
       <c r="F57">
-        <v>0.8815592115879625</v>
+        <v>0.7225491184161806</v>
       </c>
       <c r="G57">
-        <v>-6.392211042262116</v>
+        <v>-4.759870421577054</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.263158118331591</v>
       </c>
       <c r="E58">
-        <v>-8.433841125540891</v>
+        <v>-7.889414394916738</v>
       </c>
       <c r="F58">
-        <v>0.1910205474706554</v>
+        <v>0.684334045022831</v>
       </c>
       <c r="G58">
-        <v>-5.489488174068109</v>
+        <v>-5.673438636957713</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.857985708760785</v>
       </c>
       <c r="E59">
-        <v>-7.164758927261311</v>
+        <v>-8.159297860351868</v>
       </c>
       <c r="F59">
-        <v>0.03414101525887387</v>
+        <v>0.9370333198186398</v>
       </c>
       <c r="G59">
-        <v>-5.569768903395436</v>
+        <v>-5.116479076521807</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.416692470928389</v>
       </c>
       <c r="E60">
-        <v>-7.185232158249989</v>
+        <v>-7.81989779042499</v>
       </c>
       <c r="F60">
-        <v>0.4362264107407399</v>
+        <v>0.6341093010236942</v>
       </c>
       <c r="G60">
-        <v>-5.630080422029878</v>
+        <v>-6.254449310736424</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.942337123576844</v>
       </c>
       <c r="E61">
-        <v>-5.785277061148737</v>
+        <v>-7.744888146961938</v>
       </c>
       <c r="F61">
-        <v>0.2607856501344298</v>
+        <v>0.4696452368718804</v>
       </c>
       <c r="G61">
-        <v>-4.414961234568086</v>
+        <v>-5.761466042846934</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.434623862814004</v>
       </c>
       <c r="E62">
-        <v>-6.884718094626977</v>
+        <v>-7.232468670623999</v>
       </c>
       <c r="F62">
-        <v>0.681239264405972</v>
+        <v>0.6158106650958531</v>
       </c>
       <c r="G62">
-        <v>-5.489769570438948</v>
+        <v>-6.068234434697959</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.904005432221063</v>
       </c>
       <c r="E63">
-        <v>-7.6495184843604</v>
+        <v>-7.526937221446771</v>
       </c>
       <c r="F63">
-        <v>0.6397612518129953</v>
+        <v>0.4195273522677047</v>
       </c>
       <c r="G63">
-        <v>-4.492120119451879</v>
+        <v>-5.73650121893529</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.352706677406027</v>
       </c>
       <c r="E64">
-        <v>-6.375817242592998</v>
+        <v>-6.470715943897737</v>
       </c>
       <c r="F64">
-        <v>0.6171410231447492</v>
+        <v>0.7010496708439222</v>
       </c>
       <c r="G64">
-        <v>-5.190963040609869</v>
+        <v>-5.840078257222467</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.778645043885036</v>
       </c>
       <c r="E65">
-        <v>-6.677970613806787</v>
+        <v>-6.848748425584051</v>
       </c>
       <c r="F65">
-        <v>0.3402617038612228</v>
+        <v>0.7335216730336629</v>
       </c>
       <c r="G65">
-        <v>-6.018963585436986</v>
+        <v>-5.517108055502248</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.192217166893966</v>
       </c>
       <c r="E66">
-        <v>-7.456913427866165</v>
+        <v>-7.147106935579413</v>
       </c>
       <c r="F66">
-        <v>0.2233335031190586</v>
+        <v>0.1476364614838369</v>
       </c>
       <c r="G66">
-        <v>-4.327248330505095</v>
+        <v>-5.446020711137479</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.596828073668575</v>
       </c>
       <c r="E67">
-        <v>-4.965981015207008</v>
+        <v>-6.462958667922598</v>
       </c>
       <c r="F67">
-        <v>0.009333896647237078</v>
+        <v>0.1579256129940096</v>
       </c>
       <c r="G67">
-        <v>-5.095758371991509</v>
+        <v>-5.929810594064413</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.9911841557625404</v>
       </c>
       <c r="E68">
-        <v>-5.746576722279186</v>
+        <v>-6.122503463551933</v>
       </c>
       <c r="F68">
-        <v>0.1631683502863277</v>
+        <v>-0.07691323223003906</v>
       </c>
       <c r="G68">
-        <v>-5.349412371210467</v>
+        <v>-5.286985413976431</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.3860861291724024</v>
       </c>
       <c r="E69">
-        <v>-5.967570782327507</v>
+        <v>-6.674157638692328</v>
       </c>
       <c r="F69">
-        <v>0.3356303017121707</v>
+        <v>0.5176739788861957</v>
       </c>
       <c r="G69">
-        <v>-3.991168368449363</v>
+        <v>-4.969514028396941</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.2133641043340275</v>
       </c>
       <c r="E70">
-        <v>-4.053117639318795</v>
+        <v>-6.789583912673838</v>
       </c>
       <c r="F70">
-        <v>0.187101541288011</v>
+        <v>0.08959772777409238</v>
       </c>
       <c r="G70">
-        <v>-4.150753216169931</v>
+        <v>-5.012474977860063</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.8082160707007914</v>
       </c>
       <c r="E71">
-        <v>-4.786703257717346</v>
+        <v>-6.085686969869573</v>
       </c>
       <c r="F71">
-        <v>0.2279996966990282</v>
+        <v>0.4670425064922843</v>
       </c>
       <c r="G71">
-        <v>-5.564776600722214</v>
+        <v>-4.341251938136212</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.389283647254019</v>
       </c>
       <c r="E72">
-        <v>-7.065349865844932</v>
+        <v>-6.569703857231404</v>
       </c>
       <c r="F72">
-        <v>-0.1529432775611861</v>
+        <v>0.0806894647243865</v>
       </c>
       <c r="G72">
-        <v>-4.047924361174628</v>
+        <v>-4.91732989906141</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.950628136221934</v>
       </c>
       <c r="E73">
-        <v>-6.627591340471453</v>
+        <v>-6.007647777295389</v>
       </c>
       <c r="F73">
-        <v>-0.1574686486826798</v>
+        <v>0.1004046089110147</v>
       </c>
       <c r="G73">
-        <v>-3.62111227752409</v>
+        <v>-4.537249476243224</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>2.493299654038237</v>
       </c>
       <c r="E74">
-        <v>-6.159012021001772</v>
+        <v>-6.825689435936994</v>
       </c>
       <c r="F74">
-        <v>-0.2532154949352606</v>
+        <v>-0.2712879865621374</v>
       </c>
       <c r="G74">
-        <v>-3.755368141323694</v>
+        <v>-2.947376533735933</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>3.010071984595312</v>
       </c>
       <c r="E75">
-        <v>-6.606266756369334</v>
+        <v>-7.291261848665583</v>
       </c>
       <c r="F75">
-        <v>-0.4005099879292491</v>
+        <v>-0.1507431337393506</v>
       </c>
       <c r="G75">
-        <v>-3.453433145960005</v>
+        <v>-3.124470856813705</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>3.494605324830527</v>
       </c>
       <c r="E76">
-        <v>-7.124985340051943</v>
+        <v>-8.042870793614663</v>
       </c>
       <c r="F76">
-        <v>-0.01495963417466402</v>
+        <v>-0.1876734092909581</v>
       </c>
       <c r="G76">
-        <v>-2.526526742601622</v>
+        <v>-3.301515521708389</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>3.949321012967651</v>
       </c>
       <c r="E77">
-        <v>-8.250677937352648</v>
+        <v>-8.113062140733554</v>
       </c>
       <c r="F77">
-        <v>-0.6896632270200558</v>
+        <v>-0.4658027349853089</v>
       </c>
       <c r="G77">
-        <v>-2.909927642595697</v>
+        <v>-3.190900263604721</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>4.371340762252961</v>
       </c>
       <c r="E78">
-        <v>-9.317446030865547</v>
+        <v>-8.665816735057813</v>
       </c>
       <c r="F78">
-        <v>-0.7452649038307642</v>
+        <v>-0.4243172670857069</v>
       </c>
       <c r="G78">
-        <v>-1.981160712644244</v>
+        <v>-2.554537268409395</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>4.757456788444405</v>
       </c>
       <c r="E79">
-        <v>-9.694541118432273</v>
+        <v>-10.02530538842652</v>
       </c>
       <c r="F79">
-        <v>-0.3808743670132896</v>
+        <v>-0.7480556736107957</v>
       </c>
       <c r="G79">
-        <v>-2.502346517982785</v>
+        <v>-1.995200736276293</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>5.116273079754289</v>
       </c>
       <c r="E80">
-        <v>-8.721041475581353</v>
+        <v>-9.97597672106097</v>
       </c>
       <c r="F80">
-        <v>-0.913356388839437</v>
+        <v>-0.4505425506909365</v>
       </c>
       <c r="G80">
-        <v>-0.7021546173655956</v>
+        <v>-2.134578014025149</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>5.450257175383856</v>
       </c>
       <c r="E81">
-        <v>-10.52102838109818</v>
+        <v>-10.41640704609897</v>
       </c>
       <c r="F81">
-        <v>-0.8986081355999946</v>
+        <v>-0.2821172336189354</v>
       </c>
       <c r="G81">
-        <v>-0.2896010533526988</v>
+        <v>-0.7564740485739573</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>5.758243115013977</v>
       </c>
       <c r="E82">
-        <v>-12.03007894551822</v>
+        <v>-10.86306402289752</v>
       </c>
       <c r="F82">
-        <v>-0.8222533702469502</v>
+        <v>-0.7266001295108857</v>
       </c>
       <c r="G82">
-        <v>-0.3534449240775436</v>
+        <v>-1.086724139935033</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>6.047696377777267</v>
       </c>
       <c r="E83">
-        <v>-12.63156897711303</v>
+        <v>-11.94787355685698</v>
       </c>
       <c r="F83">
-        <v>-1.050575449113175</v>
+        <v>-0.7484971934364878</v>
       </c>
       <c r="G83">
-        <v>0.01203268236691685</v>
+        <v>0.06304487858154657</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>6.320628931380105</v>
       </c>
       <c r="E84">
-        <v>-13.71627435617031</v>
+        <v>-12.84885874542308</v>
       </c>
       <c r="F84">
-        <v>-0.9645461808628353</v>
+        <v>-1.003637666968347</v>
       </c>
       <c r="G84">
-        <v>-0.2319909398783016</v>
+        <v>-0.40310972825769</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>6.57120265621596</v>
       </c>
       <c r="E85">
-        <v>-14.08305357994756</v>
+        <v>-14.64055854350587</v>
       </c>
       <c r="F85">
-        <v>-0.8842169087111589</v>
+        <v>-1.052645539252771</v>
       </c>
       <c r="G85">
-        <v>0.0375106408371479</v>
+        <v>0.1891005210803756</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>6.801096692688157</v>
       </c>
       <c r="E86">
-        <v>-13.3909080271932</v>
+        <v>-14.43103057964497</v>
       </c>
       <c r="F86">
-        <v>-1.180841193407814</v>
+        <v>-1.211193403413791</v>
       </c>
       <c r="G86">
-        <v>0.6038820822412019</v>
+        <v>0.2080633259293209</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>7.007758353990194</v>
       </c>
       <c r="E87">
-        <v>-15.36494683119484</v>
+        <v>-15.50582312909946</v>
       </c>
       <c r="F87">
-        <v>-1.906105847417879</v>
+        <v>-1.489364975845684</v>
       </c>
       <c r="G87">
-        <v>1.239874296336129</v>
+        <v>0.9872333240521876</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>7.182618715678149</v>
       </c>
       <c r="E88">
-        <v>-16.84027384967976</v>
+        <v>-16.82714580353152</v>
       </c>
       <c r="F88">
-        <v>-0.9914929724759032</v>
+        <v>-1.102691355892903</v>
       </c>
       <c r="G88">
-        <v>0.4547353846059564</v>
+        <v>1.146182547029215</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>7.321027606678006</v>
       </c>
       <c r="E89">
-        <v>-18.52761043578178</v>
+        <v>-18.90317942760792</v>
       </c>
       <c r="F89">
-        <v>-1.840509089524992</v>
+        <v>-1.493636866541922</v>
       </c>
       <c r="G89">
-        <v>1.1406175199777</v>
+        <v>0.6527060078543733</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>7.417741901078796</v>
       </c>
       <c r="E90">
-        <v>-19.10061636586834</v>
+        <v>-20.62599207908603</v>
       </c>
       <c r="F90">
-        <v>-1.091129832052031</v>
+        <v>-1.629523083664555</v>
       </c>
       <c r="G90">
-        <v>0.7311758687717183</v>
+        <v>0.8533482413529822</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>7.463230420556394</v>
       </c>
       <c r="E91">
-        <v>-22.12569587315424</v>
+        <v>-21.80831777232666</v>
       </c>
       <c r="F91">
-        <v>-1.36808701787142</v>
+        <v>-1.444040853401509</v>
       </c>
       <c r="G91">
-        <v>0.6998415552425165</v>
+        <v>0.5449113345501642</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>7.451041895570201</v>
       </c>
       <c r="E92">
-        <v>-23.89158789786732</v>
+        <v>-23.41228515194747</v>
       </c>
       <c r="F92">
-        <v>-1.742493344956143</v>
+        <v>-1.864598841965805</v>
       </c>
       <c r="G92">
-        <v>1.797797225523963</v>
+        <v>1.10704858820949</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>7.375507558222871</v>
       </c>
       <c r="E93">
-        <v>-25.67912602833706</v>
+        <v>-26.02072240815766</v>
       </c>
       <c r="F93">
-        <v>-2.059545998173237</v>
+        <v>-1.92389255229079</v>
       </c>
       <c r="G93">
-        <v>1.296898443250075</v>
+        <v>0.8427313218085395</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>7.229354427913979</v>
       </c>
       <c r="E94">
-        <v>-26.6715863918581</v>
+        <v>-27.48528524392635</v>
       </c>
       <c r="F94">
-        <v>-1.917185261430323</v>
+        <v>-1.743593416867061</v>
       </c>
       <c r="G94">
-        <v>1.181171702833772</v>
+        <v>0.3532340583719017</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>7.01048193417467</v>
       </c>
       <c r="E95">
-        <v>-28.05953650436502</v>
+        <v>-29.25617217546989</v>
       </c>
       <c r="F95">
-        <v>-1.715161362500774</v>
+        <v>-2.19880201389046</v>
       </c>
       <c r="G95">
-        <v>0.2124762831331694</v>
+        <v>0.9607622019201751</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>6.711624964260184</v>
       </c>
       <c r="E96">
-        <v>-30.65262902640021</v>
+        <v>-31.29350546067673</v>
       </c>
       <c r="F96">
-        <v>-2.206033661316899</v>
+        <v>-1.834435499727666</v>
       </c>
       <c r="G96">
-        <v>0.6749661160604328</v>
+        <v>-0.0397111444118918</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>6.343288499057321</v>
       </c>
       <c r="E97">
-        <v>-33.6361394065327</v>
+        <v>-33.8497973386886</v>
       </c>
       <c r="F97">
-        <v>-2.212373985417927</v>
+        <v>-2.309494264824349</v>
       </c>
       <c r="G97">
-        <v>0.0577446951731734</v>
+        <v>0.1524196765052508</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>5.888129482406343</v>
       </c>
       <c r="E98">
-        <v>-36.21749185970301</v>
+        <v>-35.84695173826239</v>
       </c>
       <c r="F98">
-        <v>-2.595828569643429</v>
+        <v>-2.141341480627869</v>
       </c>
       <c r="G98">
-        <v>-1.196005248186375</v>
+        <v>-0.6871743988003934</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.38013384178188</v>
       </c>
       <c r="E99">
-        <v>-38.18956077751131</v>
+        <v>-37.57213051740951</v>
       </c>
       <c r="F99">
-        <v>-2.635456837825954</v>
+        <v>-2.444808908439051</v>
       </c>
       <c r="G99">
-        <v>0.4187894811405498</v>
+        <v>-0.7325983941447335</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.779451293982113</v>
       </c>
       <c r="E100">
-        <v>-39.84981482481047</v>
+        <v>-40.66746929892441</v>
       </c>
       <c r="F100">
-        <v>-2.578697103386132</v>
+        <v>-2.697686282226462</v>
       </c>
       <c r="G100">
-        <v>-1.064563348095152</v>
+        <v>-1.079960695398302</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>4.165554475773337</v>
       </c>
       <c r="E101">
-        <v>-41.67440719384797</v>
+        <v>-42.72686078102262</v>
       </c>
       <c r="F101">
-        <v>-2.568486646779226</v>
+        <v>-2.749904078196734</v>
       </c>
       <c r="G101">
-        <v>-1.021311070624574</v>
+        <v>-1.454929635903853</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.421070165099403</v>
       </c>
       <c r="E102">
-        <v>-44.11250590025963</v>
+        <v>-44.49695522961482</v>
       </c>
       <c r="F102">
-        <v>-2.977238743118822</v>
+        <v>-2.635935634184773</v>
       </c>
       <c r="G102">
-        <v>-1.709149738410027</v>
+        <v>-1.604003501537234</v>
       </c>
     </row>
   </sheetData>
